--- a/CMSDMS 接口字段需求清单.xlsx
+++ b/CMSDMS 接口字段需求清单.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="69">
   <si>
     <t>实体</t>
   </si>
@@ -40,6 +40,9 @@
     <t>描述</t>
   </si>
   <si>
+    <t>样例数据</t>
+  </si>
+  <si>
     <t>现有接口是否满足</t>
   </si>
   <si>
@@ -52,6 +55,9 @@
     <t>Device ID</t>
   </si>
   <si>
+    <t>681c395168ebf414f4f2c149</t>
+  </si>
+  <si>
     <t>是</t>
   </si>
   <si>
@@ -61,18 +67,27 @@
     <t>Device Code</t>
   </si>
   <si>
+    <t>CAHK03L002</t>
+  </si>
+  <si>
     <t>device_name</t>
   </si>
   <si>
     <t>Device Name</t>
   </si>
   <si>
+    <t>H002 (Mt. Parker Lower Catchwater CH3100)</t>
+  </si>
+  <si>
     <t>region</t>
   </si>
   <si>
     <t>Region</t>
   </si>
   <si>
+    <t>HK&amp;I</t>
+  </si>
+  <si>
     <t>否</t>
   </si>
   <si>
@@ -82,12 +97,18 @@
     <t>Device Type Code</t>
   </si>
   <si>
+    <t>ca001</t>
+  </si>
+  <si>
     <t>type_desc</t>
   </si>
   <si>
     <t>Device Type Code Description</t>
   </si>
   <si>
+    <t>Level Monitoring Point</t>
+  </si>
+  <si>
     <t>status</t>
   </si>
   <si>
@@ -100,24 +121,36 @@
     <t>Business Code</t>
   </si>
   <si>
+    <t>ca</t>
+  </si>
+  <si>
     <t>business_desc</t>
   </si>
   <si>
     <t>Business Code Description</t>
   </si>
   <si>
+    <t>Catchwater</t>
+  </si>
+  <si>
     <t>coordinate_x</t>
   </si>
   <si>
     <t>X-Axis Coordinate(HK80)</t>
   </si>
   <si>
+    <t>114.2353486006546</t>
+  </si>
+  <si>
     <t>coordinate_y</t>
   </si>
   <si>
     <t>Y-Axis Coordinate(HK80)</t>
   </si>
   <si>
+    <t>22.277590238622317</t>
+  </si>
+  <si>
     <t>设备监测通道信息</t>
   </si>
   <si>
@@ -127,24 +160,36 @@
     <t>Sensor ID</t>
   </si>
   <si>
+    <t>68303e9167ad746e6928c5e6</t>
+  </si>
+  <si>
     <t>sensor_code</t>
   </si>
   <si>
     <t>Sensor Code</t>
   </si>
   <si>
+    <t>CAHK03L00203</t>
+  </si>
+  <si>
     <t>sensor_name</t>
   </si>
   <si>
     <t>Sensor Name</t>
   </si>
   <si>
+    <t>Water Level</t>
+  </si>
+  <si>
     <t>unit</t>
   </si>
   <si>
     <t>Unit</t>
   </si>
   <si>
+    <t>M</t>
+  </si>
+  <si>
     <t>引水渠图像实时数</t>
   </si>
   <si>
@@ -154,6 +199,9 @@
     <t>ID</t>
   </si>
   <si>
+    <t>6a586be2e0cb0a733182066b</t>
+  </si>
+  <si>
     <t>utc_time</t>
   </si>
   <si>
@@ -166,7 +214,16 @@
     <t>Photo URL</t>
   </si>
   <si>
+    <t>1028/1784179682453.png</t>
+  </si>
+  <si>
     <t>设备通道监测实时数据</t>
+  </si>
+  <si>
+    <t>e000c9b242324fb5b0582859b2e8ff6e</t>
+  </si>
+  <si>
+    <t>C021028010004601</t>
   </si>
   <si>
     <t>sensor_value</t>
@@ -191,13 +248,19 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF555555"/>
+      <name val="SourceHanSansCN-Regular"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -344,7 +407,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -353,6 +416,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF8F8F8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -538,12 +607,21 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFE6E6E6"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -664,55 +742,52 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -727,79 +802,88 @@
     <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -809,6 +893,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1121,15 +1208,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <dimension ref="A1:E27"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="21.375" customWidth="1"/>
     <col min="2" max="2" width="28.125" customWidth="1"/>
     <col min="3" max="3" width="36.375" customWidth="1"/>
+    <col min="4" max="4" width="22.15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1142,325 +1230,404 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="D2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="1"/>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
         <v>9</v>
       </c>
-      <c r="D3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="1"/>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>14</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" s="1"/>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>17</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" s="1"/>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+        <v>21</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="1"/>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+        <v>24</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" s="1"/>
       <c r="B8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1</v>
+      </c>
+      <c r="E8" t="s">
         <v>19</v>
       </c>
-      <c r="C8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" s="1"/>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
+        <v>29</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" ht="14.25" spans="1:5">
       <c r="A10" s="1"/>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
+        <v>32</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" s="3"/>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" s="1"/>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
-      </c>
-      <c r="D11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
+        <v>35</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12" s="1"/>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="C12" t="s">
-        <v>28</v>
-      </c>
-      <c r="D12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="2" t="s">
-        <v>29</v>
+        <v>38</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E12" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="4" t="s">
+        <v>40</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="C13" t="s">
-        <v>31</v>
-      </c>
-      <c r="D13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="4"/>
+      <c r="B14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="2"/>
-      <c r="B14" t="s">
-        <v>5</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="D14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="4"/>
+      <c r="B15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="4"/>
+      <c r="B16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="4"/>
+      <c r="B17" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="4"/>
+      <c r="B18" t="s">
+        <v>50</v>
+      </c>
+      <c r="C18" t="s">
+        <v>51</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E18" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" t="s">
+        <v>55</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E19" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5"/>
+      <c r="B20" t="s">
         <v>6</v>
       </c>
-      <c r="D14" t="s">
+      <c r="C20" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="2"/>
-      <c r="B15" t="s">
+      <c r="D20" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C15" t="s">
+      <c r="E20" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5"/>
+      <c r="B21" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E21" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5"/>
+      <c r="B22" t="s">
+        <v>57</v>
+      </c>
+      <c r="C22" t="s">
+        <v>58</v>
+      </c>
+      <c r="D22" s="2">
+        <v>46219.5625231481</v>
+      </c>
+      <c r="E22" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5"/>
+      <c r="B23" t="s">
+        <v>59</v>
+      </c>
+      <c r="C23" t="s">
+        <v>60</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E23" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B24" t="s">
+        <v>54</v>
+      </c>
+      <c r="C24" t="s">
+        <v>55</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E24" t="s">
         <v>9</v>
       </c>
-      <c r="D15" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="2"/>
-      <c r="B16" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" t="s">
-        <v>33</v>
-      </c>
-      <c r="D16" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="2"/>
-      <c r="B17" t="s">
-        <v>34</v>
-      </c>
-      <c r="C17" t="s">
-        <v>35</v>
-      </c>
-      <c r="D17" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="2"/>
-      <c r="B18" t="s">
-        <v>36</v>
-      </c>
-      <c r="C18" t="s">
-        <v>37</v>
-      </c>
-      <c r="D18" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B19" t="s">
-        <v>39</v>
-      </c>
-      <c r="C19" t="s">
-        <v>40</v>
-      </c>
-      <c r="D19" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="3"/>
-      <c r="B20" t="s">
-        <v>5</v>
-      </c>
-      <c r="C20" t="s">
-        <v>6</v>
-      </c>
-      <c r="D20" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="3"/>
-      <c r="B21" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" t="s">
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6"/>
+      <c r="B25" t="s">
+        <v>44</v>
+      </c>
+      <c r="C25" t="s">
+        <v>45</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E25" t="s">
         <v>9</v>
       </c>
-      <c r="D21" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="3"/>
-      <c r="B22" t="s">
-        <v>41</v>
-      </c>
-      <c r="C22" t="s">
-        <v>42</v>
-      </c>
-      <c r="D22" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="3"/>
-      <c r="B23" t="s">
-        <v>43</v>
-      </c>
-      <c r="C23" t="s">
-        <v>44</v>
-      </c>
-      <c r="D23" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B24" t="s">
-        <v>39</v>
-      </c>
-      <c r="C24" t="s">
-        <v>40</v>
-      </c>
-      <c r="D24" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="4"/>
-      <c r="B25" t="s">
-        <v>32</v>
-      </c>
-      <c r="C25" t="s">
-        <v>33</v>
-      </c>
-      <c r="D25" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" s="4"/>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6"/>
       <c r="B26" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="C26" t="s">
-        <v>47</v>
-      </c>
-      <c r="D26" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" s="4"/>
+        <v>66</v>
+      </c>
+      <c r="D26" s="2">
+        <v>1800.56</v>
+      </c>
+      <c r="E26" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6"/>
       <c r="B27" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="C27" t="s">
-        <v>49</v>
-      </c>
-      <c r="D27" t="s">
-        <v>7</v>
+        <v>68</v>
+      </c>
+      <c r="D27" s="2">
+        <v>46219.5625231481</v>
+      </c>
+      <c r="E27" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
